--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19629-2026 artfynd.xlsx
+++ b/artfynd/A 19629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>122807287</v>
       </c>
       <c r="B2" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
